--- a/data/raw/Employee_Data_Raw.xlsx
+++ b/data/raw/Employee_Data_Raw.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\LN2PEPF0000F936\EXCELCNV\55e45fb9-2000-4933-92c8-627292066b08\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\LN2PEPF0000BD36\EXCELCNV\e8dbf83b-4380-4b61-9fb7-cfd2268d3df0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{8D578351-F180-401D-9156-FD1901C8E519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5A49B47-553F-4548-AC95-8F2D66B1A765}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C71371E-356D-468C-9255-A414D5437168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RAW_Employee_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="CLEAN_Reference_Answer" sheetId="4" state="hidden" r:id="rId2"/>
+    <sheet name="Pay_Grades_Reference" sheetId="2" r:id="rId2"/>
+    <sheet name="CLEAN_Reference_Answer" sheetId="4" state="hidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5443" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5521" uniqueCount="660">
   <si>
     <t>Employee_ID</t>
   </si>
@@ -1888,6 +1889,57 @@
   </si>
   <si>
     <t>27/12/2018</t>
+  </si>
+  <si>
+    <t>Pay Grades Reference Table</t>
+  </si>
+  <si>
+    <t>Pay_Grade</t>
+  </si>
+  <si>
+    <t>Grade_Label</t>
+  </si>
+  <si>
+    <t>Grade_Min_£</t>
+  </si>
+  <si>
+    <t>Grade_Max_£</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>Grade 1 — Entry</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>Grade 2 — Foundation</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>Grade 3 — Developing</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>Grade 4 — Established</t>
+  </si>
+  <si>
+    <t>G5</t>
+  </si>
+  <si>
+    <t>Grade 5 — Advanced</t>
+  </si>
+  <si>
+    <t>G6</t>
+  </si>
+  <si>
+    <t>Grade 6 — Senior</t>
   </si>
   <si>
     <t>Pay_Position_Flag</t>
@@ -1972,7 +2024,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="\£#,##0"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1988,6 +2043,24 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -2041,7 +2114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2052,6 +2125,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14613,6 +14696,475 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="5" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="30" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" customHeight="1">
+      <c r="A2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="D5" s="4">
+        <v>22000</v>
+      </c>
+      <c r="E5" s="4">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="D6" s="5">
+        <v>28000</v>
+      </c>
+      <c r="E6" s="5">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="D7" s="4">
+        <v>26000</v>
+      </c>
+      <c r="E7" s="4">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="D8" s="5">
+        <v>26000</v>
+      </c>
+      <c r="E8" s="5">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="D9" s="4">
+        <v>26000</v>
+      </c>
+      <c r="E9" s="4">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D10" s="5">
+        <v>28000</v>
+      </c>
+      <c r="E10" s="5">
+        <v>58000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="D11" s="4">
+        <v>30000</v>
+      </c>
+      <c r="E11" s="4">
+        <v>62000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D12" s="5">
+        <v>30000</v>
+      </c>
+      <c r="E12" s="5">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="D13" s="4">
+        <v>32000</v>
+      </c>
+      <c r="E13" s="4">
+        <v>68000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D14" s="5">
+        <v>28000</v>
+      </c>
+      <c r="E14" s="5">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="D15" s="4">
+        <v>28000</v>
+      </c>
+      <c r="E15" s="4">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D16" s="5">
+        <v>30000</v>
+      </c>
+      <c r="E16" s="5">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="D17" s="4">
+        <v>28000</v>
+      </c>
+      <c r="E17" s="4">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D18" s="5">
+        <v>28000</v>
+      </c>
+      <c r="E18" s="5">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="D19" s="4">
+        <v>33000</v>
+      </c>
+      <c r="E19" s="4">
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="D20" s="5">
+        <v>32000</v>
+      </c>
+      <c r="E20" s="5">
+        <v>78000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="D21" s="4">
+        <v>30000</v>
+      </c>
+      <c r="E21" s="4">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="D22" s="5">
+        <v>38000</v>
+      </c>
+      <c r="E22" s="5">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="D23" s="4">
+        <v>38000</v>
+      </c>
+      <c r="E23" s="4">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="D24" s="5">
+        <v>40000</v>
+      </c>
+      <c r="E24" s="5">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="D25" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E25" s="4">
+        <v>98000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="D26" s="5">
+        <v>36000</v>
+      </c>
+      <c r="E26" s="5">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="D27" s="4">
+        <v>43000</v>
+      </c>
+      <c r="E27" s="4">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="D28" s="5">
+        <v>43000</v>
+      </c>
+      <c r="E28" s="5">
+        <v>115000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="9"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A30:E30"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:S257"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14680,16 +15232,16 @@
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>617</v>
+        <v>634</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>619</v>
+        <v>636</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>620</v>
+        <v>637</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -14739,16 +15291,16 @@
         <v>0.98899999999999999</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q2" s="2">
         <v>-1100</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -14798,16 +15350,16 @@
         <v>0.86299999999999999</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q3" s="3">
         <v>-8500</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -14857,16 +15409,16 @@
         <v>1.004</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q4" s="2">
         <v>200</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -14916,16 +15468,16 @@
         <v>1.155</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q5" s="3">
         <v>12700</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -14975,16 +15527,16 @@
         <v>1.0269999999999999</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q6" s="2">
         <v>1200</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -15034,16 +15586,16 @@
         <v>1.0880000000000001</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q7" s="3">
         <v>3600</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -15093,16 +15645,16 @@
         <v>1.018</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q8" s="2">
         <v>1100</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -15152,16 +15704,16 @@
         <v>0.88800000000000001</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q9" s="3">
         <v>-9200</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -15211,16 +15763,16 @@
         <v>0.89</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q10" s="2">
         <v>-4600</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -15270,16 +15822,16 @@
         <v>0.93100000000000005</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q11" s="3">
         <v>-6000</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -15329,16 +15881,16 @@
         <v>1.036</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q12" s="2">
         <v>2100</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -15364,7 +15916,7 @@
         <v>28</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>631</v>
+        <v>648</v>
       </c>
       <c r="I13" s="3">
         <v>5</v>
@@ -15388,16 +15940,16 @@
         <v>0.84399999999999997</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q13" s="3">
         <v>-9700</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -15447,16 +15999,16 @@
         <v>1.1459999999999999</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q14" s="2">
         <v>10500</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -15506,16 +16058,16 @@
         <v>0.93700000000000006</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q15" s="3">
         <v>-5200</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -15565,16 +16117,16 @@
         <v>0.81499999999999995</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q16" s="2">
         <v>-8900</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -15624,16 +16176,16 @@
         <v>0.995</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q17" s="3">
         <v>-200</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -15683,16 +16235,16 @@
         <v>0.89900000000000002</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q18" s="2">
         <v>-5100</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -15742,16 +16294,16 @@
         <v>0.88200000000000001</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q19" s="3">
         <v>-4700</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -15801,16 +16353,16 @@
         <v>0.86899999999999999</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q20" s="2">
         <v>-5900</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -15860,16 +16412,16 @@
         <v>0.82599999999999996</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q21" s="3">
         <v>-14800</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -15919,16 +16471,16 @@
         <v>0.94199999999999995</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q22" s="2">
         <v>-4800</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -15978,16 +16530,16 @@
         <v>0.86199999999999999</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q23" s="3">
         <v>-17400</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -16037,16 +16589,16 @@
         <v>0.95199999999999996</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q24" s="2">
         <v>-1900</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -16096,16 +16648,16 @@
         <v>0.92600000000000005</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q25" s="3">
         <v>-7500</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -16155,16 +16707,16 @@
         <v>0.83</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q26" s="2">
         <v>-6800</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -16214,16 +16766,16 @@
         <v>1.054</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q27" s="3">
         <v>4300</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -16273,16 +16825,16 @@
         <v>0.90900000000000003</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q28" s="2">
         <v>-7400</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -16332,16 +16884,16 @@
         <v>0.91800000000000004</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q29" s="3">
         <v>-8100</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -16391,16 +16943,16 @@
         <v>1.099</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q30" s="2">
         <v>8300</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -16450,16 +17002,16 @@
         <v>1.1539999999999999</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q31" s="3">
         <v>6700</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -16509,16 +17061,16 @@
         <v>0.82499999999999996</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q32" s="2">
         <v>-8500</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -16568,16 +17120,16 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q33" s="3">
         <v>5700</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -16627,16 +17179,16 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q34" s="2">
         <v>-5500</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -16686,16 +17238,16 @@
         <v>1.056</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q35" s="3">
         <v>3200</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -16745,16 +17297,16 @@
         <v>0.99199999999999999</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q36" s="2">
         <v>-500</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -16804,16 +17356,16 @@
         <v>0.88700000000000001</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q37" s="3">
         <v>-3800</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -16863,16 +17415,16 @@
         <v>0.78800000000000003</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q38" s="2">
         <v>-24400</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -16922,16 +17474,16 @@
         <v>0.92400000000000004</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q39" s="3">
         <v>-6800</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -16981,16 +17533,16 @@
         <v>0.90200000000000002</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q40" s="2">
         <v>-6500</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -17040,16 +17592,16 @@
         <v>0.92500000000000004</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q41" s="3">
         <v>-6600</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -17099,16 +17651,16 @@
         <v>0.98899999999999999</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q42" s="2">
         <v>-600</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -17134,7 +17686,7 @@
         <v>37</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
       <c r="I43" s="3">
         <v>4.5</v>
@@ -17158,16 +17710,16 @@
         <v>0.98499999999999999</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q43" s="3">
         <v>-1200</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="44" spans="1:19">
@@ -17217,16 +17769,16 @@
         <v>1.161</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q44" s="2">
         <v>9300</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="45" spans="1:19">
@@ -17276,16 +17828,16 @@
         <v>0.81799999999999995</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q45" s="3">
         <v>-20900</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="46" spans="1:19">
@@ -17311,7 +17863,7 @@
         <v>77</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>634</v>
+        <v>651</v>
       </c>
       <c r="I46" s="2">
         <v>7.5</v>
@@ -17335,16 +17887,16 @@
         <v>0.92600000000000005</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q46" s="2">
         <v>-3500</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="47" spans="1:19">
@@ -17394,16 +17946,16 @@
         <v>0.86499999999999999</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q47" s="3">
         <v>-11300</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="48" spans="1:19">
@@ -17453,16 +18005,16 @@
         <v>0.94499999999999995</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q48" s="2">
         <v>-3600</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="49" spans="1:19">
@@ -17512,16 +18064,16 @@
         <v>1.0920000000000001</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q49" s="3">
         <v>9100</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="50" spans="1:19">
@@ -17571,16 +18123,16 @@
         <v>0.98899999999999999</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q50" s="2">
         <v>-700</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="51" spans="1:19">
@@ -17630,16 +18182,16 @@
         <v>0.91800000000000004</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q51" s="3">
         <v>-5600</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="52" spans="1:19">
@@ -17689,16 +18241,16 @@
         <v>0.93300000000000005</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q52" s="2">
         <v>-4000</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="53" spans="1:19">
@@ -17748,16 +18300,16 @@
         <v>1.0620000000000001</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q53" s="3">
         <v>3000</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="54" spans="1:19">
@@ -17807,16 +18359,16 @@
         <v>0.96199999999999997</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q54" s="2">
         <v>-2300</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="55" spans="1:19">
@@ -17866,16 +18418,16 @@
         <v>0.84799999999999998</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q55" s="3">
         <v>-7200</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="56" spans="1:19">
@@ -17925,16 +18477,16 @@
         <v>0.878</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q56" s="2">
         <v>-9500</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="57" spans="1:19">
@@ -17984,16 +18536,16 @@
         <v>0.93799999999999994</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q57" s="3">
         <v>-3600</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="58" spans="1:19">
@@ -18019,7 +18571,7 @@
         <v>21</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>635</v>
+        <v>652</v>
       </c>
       <c r="I58" s="2">
         <v>3.1</v>
@@ -18043,16 +18595,16 @@
         <v>0.93899999999999995</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q58" s="2">
         <v>-3500</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="59" spans="1:19">
@@ -18102,16 +18654,16 @@
         <v>0.98799999999999999</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q59" s="3">
         <v>-500</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="60" spans="1:19">
@@ -18161,16 +18713,16 @@
         <v>1.03</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q60" s="2">
         <v>1500</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -18220,16 +18772,16 @@
         <v>1.012</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q61" s="3">
         <v>600</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="62" spans="1:19">
@@ -18279,16 +18831,16 @@
         <v>0.95299999999999996</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q62" s="2">
         <v>-2800</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="63" spans="1:19">
@@ -18338,16 +18890,16 @@
         <v>0.96799999999999997</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q63" s="3">
         <v>-3200</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="64" spans="1:19">
@@ -18397,16 +18949,16 @@
         <v>0.93400000000000005</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q64" s="2">
         <v>-4900</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="65" spans="1:19">
@@ -18456,16 +19008,16 @@
         <v>1.0389999999999999</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q65" s="3">
         <v>1900</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S65" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="66" spans="1:19">
@@ -18515,16 +19067,16 @@
         <v>1.119</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q66" s="2">
         <v>8100</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="67" spans="1:19">
@@ -18574,16 +19126,16 @@
         <v>0.93100000000000005</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q67" s="3">
         <v>-2900</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="68" spans="1:19">
@@ -18633,16 +19185,16 @@
         <v>0.93899999999999995</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q68" s="2">
         <v>-2000</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="69" spans="1:19">
@@ -18692,16 +19244,16 @@
         <v>1.016</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q69" s="3">
         <v>1600</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S69" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="70" spans="1:19">
@@ -18751,16 +19303,16 @@
         <v>1.1539999999999999</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q70" s="2">
         <v>10500</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="71" spans="1:19">
@@ -18810,16 +19362,16 @@
         <v>1.002</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q71" s="3">
         <v>100</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S71" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="72" spans="1:19">
@@ -18869,16 +19421,16 @@
         <v>0.79600000000000004</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q72" s="2">
         <v>-16800</v>
       </c>
       <c r="R72" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="73" spans="1:19">
@@ -18928,16 +19480,16 @@
         <v>1.1339999999999999</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q73" s="3">
         <v>4700</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S73" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="74" spans="1:19">
@@ -18987,16 +19539,16 @@
         <v>0.82899999999999996</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q74" s="2">
         <v>-8200</v>
       </c>
       <c r="R74" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="75" spans="1:19">
@@ -19022,7 +19574,7 @@
         <v>21</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>636</v>
+        <v>653</v>
       </c>
       <c r="I75" s="3">
         <v>4</v>
@@ -19046,16 +19598,16 @@
         <v>1.0449999999999999</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q75" s="3">
         <v>4600</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S75" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="76" spans="1:19">
@@ -19105,16 +19657,16 @@
         <v>1.0680000000000001</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q76" s="2">
         <v>4200</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="77" spans="1:19">
@@ -19164,16 +19716,16 @@
         <v>0.80400000000000005</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q77" s="3">
         <v>-15300</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S77" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="78" spans="1:19">
@@ -19223,16 +19775,16 @@
         <v>1.0549999999999999</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q78" s="2">
         <v>3300</v>
       </c>
       <c r="R78" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="79" spans="1:19">
@@ -19282,16 +19834,16 @@
         <v>0.92700000000000005</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q79" s="3">
         <v>-4500</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S79" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="80" spans="1:19">
@@ -19341,16 +19893,16 @@
         <v>1.01</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q80" s="2">
         <v>600</v>
       </c>
       <c r="R80" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="81" spans="1:19">
@@ -19400,16 +19952,16 @@
         <v>1.0249999999999999</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q81" s="3">
         <v>1200</v>
       </c>
       <c r="R81" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S81" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="82" spans="1:19">
@@ -19459,16 +20011,16 @@
         <v>1.0169999999999999</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q82" s="2">
         <v>700</v>
       </c>
       <c r="R82" s="2" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="83" spans="1:19">
@@ -19518,16 +20070,16 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q83" s="3">
         <v>-4600</v>
       </c>
       <c r="R83" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S83" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="84" spans="1:19">
@@ -19553,7 +20105,7 @@
         <v>21</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>637</v>
+        <v>654</v>
       </c>
       <c r="I84" s="2">
         <v>3</v>
@@ -19577,16 +20129,16 @@
         <v>0.86199999999999999</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q84" s="2">
         <v>-10300</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="85" spans="1:19">
@@ -19636,16 +20188,16 @@
         <v>0.86899999999999999</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q85" s="3">
         <v>-8100</v>
       </c>
       <c r="R85" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S85" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="86" spans="1:19">
@@ -19695,16 +20247,16 @@
         <v>0.873</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q86" s="2">
         <v>-8200</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="87" spans="1:19">
@@ -19754,16 +20306,16 @@
         <v>0.79700000000000004</v>
       </c>
       <c r="P87" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q87" s="3">
         <v>-13800</v>
       </c>
       <c r="R87" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S87" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="88" spans="1:19">
@@ -19813,16 +20365,16 @@
         <v>1.048</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q88" s="2">
         <v>3000</v>
       </c>
       <c r="R88" s="2" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="89" spans="1:19">
@@ -19872,16 +20424,16 @@
         <v>0.85599999999999998</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q89" s="3">
         <v>-11200</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S89" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="90" spans="1:19">
@@ -19931,16 +20483,16 @@
         <v>0.86</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q90" s="2">
         <v>-13800</v>
       </c>
       <c r="R90" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S90" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="91" spans="1:19">
@@ -19990,16 +20542,16 @@
         <v>1.17</v>
       </c>
       <c r="P91" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q91" s="3">
         <v>10200</v>
       </c>
       <c r="R91" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S91" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="92" spans="1:19">
@@ -20025,7 +20577,7 @@
         <v>21</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>638</v>
+        <v>655</v>
       </c>
       <c r="I92" s="2">
         <v>5.7</v>
@@ -20049,16 +20601,16 @@
         <v>0.95799999999999996</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q92" s="2">
         <v>-1500</v>
       </c>
       <c r="R92" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S92" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="93" spans="1:19">
@@ -20108,16 +20660,16 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="P93" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q93" s="3">
         <v>-2800</v>
       </c>
       <c r="R93" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S93" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="94" spans="1:19">
@@ -20167,16 +20719,16 @@
         <v>0.99199999999999999</v>
       </c>
       <c r="P94" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q94" s="2">
         <v>-600</v>
       </c>
       <c r="R94" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S94" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="95" spans="1:19">
@@ -20226,16 +20778,16 @@
         <v>0.873</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q95" s="3">
         <v>-3800</v>
       </c>
       <c r="R95" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S95" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="96" spans="1:19">
@@ -20285,16 +20837,16 @@
         <v>0.78300000000000003</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q96" s="2">
         <v>-6500</v>
       </c>
       <c r="R96" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S96" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="97" spans="1:19">
@@ -20344,16 +20896,16 @@
         <v>0.94399999999999995</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q97" s="3">
         <v>-2300</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S97" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="98" spans="1:19">
@@ -20403,16 +20955,16 @@
         <v>0.92600000000000005</v>
       </c>
       <c r="P98" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q98" s="2">
         <v>-4000</v>
       </c>
       <c r="R98" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S98" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="99" spans="1:19">
@@ -20462,16 +21014,16 @@
         <v>0.90400000000000003</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q99" s="3">
         <v>-4600</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S99" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="100" spans="1:19">
@@ -20521,16 +21073,16 @@
         <v>0.84199999999999997</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q100" s="2">
         <v>-6000</v>
       </c>
       <c r="R100" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S100" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="101" spans="1:19">
@@ -20580,16 +21132,16 @@
         <v>1.1830000000000001</v>
       </c>
       <c r="P101" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q101" s="3">
         <v>12100</v>
       </c>
       <c r="R101" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S101" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="102" spans="1:19">
@@ -20639,16 +21191,16 @@
         <v>1.1639999999999999</v>
       </c>
       <c r="P102" s="2" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q102" s="2">
         <v>12200</v>
       </c>
       <c r="R102" s="2" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S102" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="103" spans="1:19">
@@ -20698,16 +21250,16 @@
         <v>0.82199999999999995</v>
       </c>
       <c r="P103" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q103" s="3">
         <v>-6400</v>
       </c>
       <c r="R103" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S103" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="104" spans="1:19">
@@ -20757,16 +21309,16 @@
         <v>0.96299999999999997</v>
       </c>
       <c r="P104" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q104" s="2">
         <v>-2000</v>
       </c>
       <c r="R104" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S104" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="105" spans="1:19">
@@ -20816,16 +21368,16 @@
         <v>0.97299999999999998</v>
       </c>
       <c r="P105" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q105" s="3">
         <v>-800</v>
       </c>
       <c r="R105" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S105" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="106" spans="1:19">
@@ -20875,16 +21427,16 @@
         <v>1.0289999999999999</v>
       </c>
       <c r="P106" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q106" s="2">
         <v>800</v>
       </c>
       <c r="R106" s="2" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S106" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="107" spans="1:19">
@@ -20934,16 +21486,16 @@
         <v>0.97399999999999998</v>
       </c>
       <c r="P107" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q107" s="3">
         <v>-1400</v>
       </c>
       <c r="R107" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S107" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="108" spans="1:19">
@@ -20993,16 +21545,16 @@
         <v>0.90600000000000003</v>
       </c>
       <c r="P108" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q108" s="2">
         <v>-3400</v>
       </c>
       <c r="R108" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S108" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="109" spans="1:19">
@@ -21052,16 +21604,16 @@
         <v>1.125</v>
       </c>
       <c r="P109" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q109" s="3">
         <v>4500</v>
       </c>
       <c r="R109" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S109" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="110" spans="1:19">
@@ -21111,16 +21663,16 @@
         <v>0.80800000000000005</v>
       </c>
       <c r="P110" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q110" s="2">
         <v>-8200</v>
       </c>
       <c r="R110" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S110" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="111" spans="1:19">
@@ -21170,16 +21722,16 @@
         <v>1.0269999999999999</v>
       </c>
       <c r="P111" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q111" s="3">
         <v>800</v>
       </c>
       <c r="R111" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S111" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="112" spans="1:19">
@@ -21205,7 +21757,7 @@
         <v>77</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>639</v>
+        <v>656</v>
       </c>
       <c r="I112" s="2">
         <v>6.3</v>
@@ -21229,16 +21781,16 @@
         <v>0.79800000000000004</v>
       </c>
       <c r="P112" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q112" s="2">
         <v>-14600</v>
       </c>
       <c r="R112" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S112" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="113" spans="1:19">
@@ -21288,16 +21840,16 @@
         <v>1.131</v>
       </c>
       <c r="P113" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q113" s="3">
         <v>11000</v>
       </c>
       <c r="R113" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S113" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="114" spans="1:19">
@@ -21347,16 +21899,16 @@
         <v>1.008</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q114" s="2">
         <v>300</v>
       </c>
       <c r="R114" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S114" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="115" spans="1:19">
@@ -21406,16 +21958,16 @@
         <v>0.93899999999999995</v>
       </c>
       <c r="P115" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q115" s="3">
         <v>-5600</v>
       </c>
       <c r="R115" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S115" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="116" spans="1:19">
@@ -21465,16 +22017,16 @@
         <v>0.81399999999999995</v>
       </c>
       <c r="P116" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q116" s="2">
         <v>-8100</v>
       </c>
       <c r="R116" s="2" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S116" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="117" spans="1:19">
@@ -21524,16 +22076,16 @@
         <v>0.96099999999999997</v>
       </c>
       <c r="P117" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q117" s="3">
         <v>-1100</v>
       </c>
       <c r="R117" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S117" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="118" spans="1:19">
@@ -21583,16 +22135,16 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="P118" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q118" s="2">
         <v>-2600</v>
       </c>
       <c r="R118" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S118" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="119" spans="1:19">
@@ -21642,16 +22194,16 @@
         <v>1.0349999999999999</v>
       </c>
       <c r="P119" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q119" s="3">
         <v>2100</v>
       </c>
       <c r="R119" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S119" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="120" spans="1:19">
@@ -21701,16 +22253,16 @@
         <v>0.874</v>
       </c>
       <c r="P120" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q120" s="2">
         <v>-6800</v>
       </c>
       <c r="R120" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S120" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="121" spans="1:19">
@@ -21760,16 +22312,16 @@
         <v>0.874</v>
       </c>
       <c r="P121" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q121" s="3">
         <v>-3900</v>
       </c>
       <c r="R121" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S121" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="122" spans="1:19">
@@ -21819,16 +22371,16 @@
         <v>1.06</v>
       </c>
       <c r="P122" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q122" s="2">
         <v>3100</v>
       </c>
       <c r="R122" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S122" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="123" spans="1:19">
@@ -21878,16 +22430,16 @@
         <v>1.101</v>
       </c>
       <c r="P123" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q123" s="3">
         <v>3400</v>
       </c>
       <c r="R123" s="3" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S123" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="124" spans="1:19">
@@ -21937,16 +22489,16 @@
         <v>0.91900000000000004</v>
       </c>
       <c r="P124" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q124" s="2">
         <v>-5200</v>
       </c>
       <c r="R124" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S124" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="125" spans="1:19">
@@ -21996,16 +22548,16 @@
         <v>0.77400000000000002</v>
       </c>
       <c r="P125" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q125" s="3">
         <v>-16300</v>
       </c>
       <c r="R125" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S125" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="126" spans="1:19">
@@ -22055,16 +22607,16 @@
         <v>0.872</v>
       </c>
       <c r="P126" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q126" s="2">
         <v>-7200</v>
       </c>
       <c r="R126" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S126" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="127" spans="1:19">
@@ -22114,16 +22666,16 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="P127" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q127" s="3">
         <v>-2000</v>
       </c>
       <c r="R127" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S127" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="128" spans="1:19">
@@ -22173,16 +22725,16 @@
         <v>1.004</v>
       </c>
       <c r="P128" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q128" s="2">
         <v>100</v>
       </c>
       <c r="R128" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S128" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="129" spans="1:19">
@@ -22232,16 +22784,16 @@
         <v>0.93</v>
       </c>
       <c r="P129" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q129" s="3">
         <v>-5700</v>
       </c>
       <c r="R129" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S129" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="130" spans="1:19">
@@ -22291,16 +22843,16 @@
         <v>0.89200000000000002</v>
       </c>
       <c r="P130" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q130" s="2">
         <v>-5200</v>
       </c>
       <c r="R130" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S130" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="131" spans="1:19">
@@ -22350,16 +22902,16 @@
         <v>1.1419999999999999</v>
       </c>
       <c r="P131" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q131" s="3">
         <v>5400</v>
       </c>
       <c r="R131" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S131" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="132" spans="1:19">
@@ -22409,16 +22961,16 @@
         <v>0.93799999999999994</v>
       </c>
       <c r="P132" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q132" s="2">
         <v>-3500</v>
       </c>
       <c r="R132" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S132" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="133" spans="1:19">
@@ -22468,16 +23020,16 @@
         <v>0.93500000000000005</v>
       </c>
       <c r="P133" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q133" s="3">
         <v>-2900</v>
       </c>
       <c r="R133" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S133" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="134" spans="1:19">
@@ -22527,16 +23079,16 @@
         <v>1.0629999999999999</v>
       </c>
       <c r="P134" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q134" s="2">
         <v>3000</v>
       </c>
       <c r="R134" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S134" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="135" spans="1:19">
@@ -22586,16 +23138,16 @@
         <v>0.77500000000000002</v>
       </c>
       <c r="P135" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q135" s="3">
         <v>-9900</v>
       </c>
       <c r="R135" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S135" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="136" spans="1:19">
@@ -22645,16 +23197,16 @@
         <v>1</v>
       </c>
       <c r="P136" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q136" s="2">
         <v>0</v>
       </c>
       <c r="R136" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S136" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="137" spans="1:19">
@@ -22704,16 +23256,16 @@
         <v>0.995</v>
       </c>
       <c r="P137" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q137" s="3">
         <v>-300</v>
       </c>
       <c r="R137" s="3" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S137" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="138" spans="1:19">
@@ -22763,16 +23315,16 @@
         <v>0.86799999999999999</v>
       </c>
       <c r="P138" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q138" s="2">
         <v>-7300</v>
       </c>
       <c r="R138" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S138" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="139" spans="1:19">
@@ -22822,16 +23374,16 @@
         <v>0.98099999999999998</v>
       </c>
       <c r="P139" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q139" s="3">
         <v>-900</v>
       </c>
       <c r="R139" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S139" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="140" spans="1:19">
@@ -22881,16 +23433,16 @@
         <v>0.94699999999999995</v>
       </c>
       <c r="P140" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q140" s="2">
         <v>-1700</v>
       </c>
       <c r="R140" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S140" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="141" spans="1:19">
@@ -22940,16 +23492,16 @@
         <v>0.93200000000000005</v>
       </c>
       <c r="P141" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q141" s="3">
         <v>-3600</v>
       </c>
       <c r="R141" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S141" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="142" spans="1:19">
@@ -22999,16 +23551,16 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="P142" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q142" s="2">
         <v>-1900</v>
       </c>
       <c r="R142" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S142" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="143" spans="1:19">
@@ -23058,16 +23610,16 @@
         <v>1.002</v>
       </c>
       <c r="P143" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q143" s="3">
         <v>100</v>
       </c>
       <c r="R143" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S143" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="144" spans="1:19">
@@ -23117,16 +23669,16 @@
         <v>0.89100000000000001</v>
       </c>
       <c r="P144" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q144" s="2">
         <v>-5200</v>
       </c>
       <c r="R144" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S144" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="145" spans="1:19">
@@ -23176,16 +23728,16 @@
         <v>0.95799999999999996</v>
       </c>
       <c r="P145" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q145" s="3">
         <v>-1500</v>
       </c>
       <c r="R145" s="3" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S145" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="146" spans="1:19">
@@ -23235,16 +23787,16 @@
         <v>1.0960000000000001</v>
       </c>
       <c r="P146" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q146" s="2">
         <v>5400</v>
       </c>
       <c r="R146" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S146" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="147" spans="1:19">
@@ -23294,16 +23846,16 @@
         <v>0.88900000000000001</v>
       </c>
       <c r="P147" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q147" s="3">
         <v>-8000</v>
       </c>
       <c r="R147" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S147" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="148" spans="1:19">
@@ -23353,16 +23905,16 @@
         <v>0.85</v>
       </c>
       <c r="P148" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q148" s="2">
         <v>-4500</v>
       </c>
       <c r="R148" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S148" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="149" spans="1:19">
@@ -23412,16 +23964,16 @@
         <v>0.90700000000000003</v>
       </c>
       <c r="P149" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q149" s="3">
         <v>-5000</v>
       </c>
       <c r="R149" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S149" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="150" spans="1:19">
@@ -23471,16 +24023,16 @@
         <v>0.98099999999999998</v>
       </c>
       <c r="P150" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q150" s="2">
         <v>-900</v>
       </c>
       <c r="R150" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S150" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="151" spans="1:19">
@@ -23530,16 +24082,16 @@
         <v>0.86399999999999999</v>
       </c>
       <c r="P151" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q151" s="3">
         <v>-3700</v>
       </c>
       <c r="R151" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S151" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="152" spans="1:19">
@@ -23589,16 +24141,16 @@
         <v>0.996</v>
       </c>
       <c r="P152" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q152" s="2">
         <v>-200</v>
       </c>
       <c r="R152" s="2" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S152" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="153" spans="1:19">
@@ -23648,16 +24200,16 @@
         <v>0.93700000000000006</v>
       </c>
       <c r="P153" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q153" s="3">
         <v>-5400</v>
       </c>
       <c r="R153" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S153" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="154" spans="1:19">
@@ -23707,16 +24259,16 @@
         <v>0.96499999999999997</v>
       </c>
       <c r="P154" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q154" s="2">
         <v>-1800</v>
       </c>
       <c r="R154" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S154" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="155" spans="1:19">
@@ -23766,16 +24318,16 @@
         <v>0.91100000000000003</v>
       </c>
       <c r="P155" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q155" s="3">
         <v>-3100</v>
       </c>
       <c r="R155" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S155" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="156" spans="1:19">
@@ -23825,16 +24377,16 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="P156" s="2" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q156" s="2">
         <v>8000</v>
       </c>
       <c r="R156" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S156" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="157" spans="1:19">
@@ -23884,16 +24436,16 @@
         <v>1.044</v>
       </c>
       <c r="P157" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q157" s="3">
         <v>2100</v>
       </c>
       <c r="R157" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S157" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="158" spans="1:19">
@@ -23943,16 +24495,16 @@
         <v>1.155</v>
       </c>
       <c r="P158" s="2" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q158" s="2">
         <v>8100</v>
       </c>
       <c r="R158" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S158" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="159" spans="1:19">
@@ -24002,16 +24554,16 @@
         <v>1.022</v>
       </c>
       <c r="P159" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q159" s="3">
         <v>2000</v>
       </c>
       <c r="R159" s="3" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S159" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="160" spans="1:19">
@@ -24037,7 +24589,7 @@
         <v>45</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>640</v>
+        <v>657</v>
       </c>
       <c r="I160" s="2">
         <v>5.7</v>
@@ -24061,16 +24613,16 @@
         <v>0.81499999999999995</v>
       </c>
       <c r="P160" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q160" s="2">
         <v>-18500</v>
       </c>
       <c r="R160" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S160" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="161" spans="1:19">
@@ -24120,16 +24672,16 @@
         <v>0.89300000000000002</v>
       </c>
       <c r="P161" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q161" s="3">
         <v>-9600</v>
       </c>
       <c r="R161" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S161" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="162" spans="1:19">
@@ -24179,16 +24731,16 @@
         <v>1.1180000000000001</v>
       </c>
       <c r="P162" s="2" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q162" s="2">
         <v>7800</v>
       </c>
       <c r="R162" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S162" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="163" spans="1:19">
@@ -24238,16 +24790,16 @@
         <v>0.90800000000000003</v>
       </c>
       <c r="P163" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q163" s="3">
         <v>-7700</v>
       </c>
       <c r="R163" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S163" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="164" spans="1:19">
@@ -24297,16 +24849,16 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="P164" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q164" s="2">
         <v>-4700</v>
       </c>
       <c r="R164" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S164" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="165" spans="1:19">
@@ -24356,16 +24908,16 @@
         <v>1.206</v>
       </c>
       <c r="P165" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q165" s="3">
         <v>18500</v>
       </c>
       <c r="R165" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S165" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="166" spans="1:19">
@@ -24415,16 +24967,16 @@
         <v>0.98399999999999999</v>
       </c>
       <c r="P166" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q166" s="2">
         <v>-600</v>
       </c>
       <c r="R166" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S166" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="167" spans="1:19">
@@ -24474,16 +25026,16 @@
         <v>1.1759999999999999</v>
       </c>
       <c r="P167" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q167" s="3">
         <v>9900</v>
       </c>
       <c r="R167" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S167" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="168" spans="1:19">
@@ -24533,16 +25085,16 @@
         <v>0.86599999999999999</v>
       </c>
       <c r="P168" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q168" s="2">
         <v>-7000</v>
       </c>
       <c r="R168" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S168" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="169" spans="1:19">
@@ -24592,16 +25144,16 @@
         <v>0.94599999999999995</v>
       </c>
       <c r="P169" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q169" s="3">
         <v>-3900</v>
       </c>
       <c r="R169" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S169" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="170" spans="1:19">
@@ -24651,16 +25203,16 @@
         <v>0.77700000000000002</v>
       </c>
       <c r="P170" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q170" s="2">
         <v>-7500</v>
       </c>
       <c r="R170" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S170" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="171" spans="1:19">
@@ -24710,16 +25262,16 @@
         <v>1.042</v>
       </c>
       <c r="P171" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q171" s="3">
         <v>1700</v>
       </c>
       <c r="R171" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S171" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="172" spans="1:19">
@@ -24769,16 +25321,16 @@
         <v>1.0329999999999999</v>
       </c>
       <c r="P172" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q172" s="2">
         <v>2700</v>
       </c>
       <c r="R172" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S172" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="173" spans="1:19">
@@ -24828,16 +25380,16 @@
         <v>1.054</v>
       </c>
       <c r="P173" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q173" s="3">
         <v>3700</v>
       </c>
       <c r="R173" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S173" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="174" spans="1:19">
@@ -24887,16 +25439,16 @@
         <v>0.93200000000000005</v>
       </c>
       <c r="P174" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q174" s="2">
         <v>-1800</v>
       </c>
       <c r="R174" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S174" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="175" spans="1:19">
@@ -24946,16 +25498,16 @@
         <v>0.84699999999999998</v>
       </c>
       <c r="P175" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q175" s="3">
         <v>-10100</v>
       </c>
       <c r="R175" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S175" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="176" spans="1:19">
@@ -25005,16 +25557,16 @@
         <v>0.83499999999999996</v>
       </c>
       <c r="P176" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q176" s="2">
         <v>-7900</v>
       </c>
       <c r="R176" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S176" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="177" spans="1:19">
@@ -25064,16 +25616,16 @@
         <v>0.93899999999999995</v>
       </c>
       <c r="P177" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q177" s="3">
         <v>-2800</v>
       </c>
       <c r="R177" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S177" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="178" spans="1:19">
@@ -25123,16 +25675,16 @@
         <v>1.016</v>
       </c>
       <c r="P178" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q178" s="2">
         <v>600</v>
       </c>
       <c r="R178" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S178" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="179" spans="1:19">
@@ -25182,16 +25734,16 @@
         <v>0.98799999999999999</v>
       </c>
       <c r="P179" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q179" s="3">
         <v>-700</v>
       </c>
       <c r="R179" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S179" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="180" spans="1:19">
@@ -25241,16 +25793,16 @@
         <v>1.0029999999999999</v>
       </c>
       <c r="P180" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q180" s="2">
         <v>100</v>
       </c>
       <c r="R180" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S180" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="181" spans="1:19">
@@ -25300,16 +25852,16 @@
         <v>0.82599999999999996</v>
       </c>
       <c r="P181" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q181" s="3">
         <v>-8700</v>
       </c>
       <c r="R181" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S181" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="182" spans="1:19">
@@ -25359,16 +25911,16 @@
         <v>0.94699999999999995</v>
       </c>
       <c r="P182" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q182" s="2">
         <v>-1800</v>
       </c>
       <c r="R182" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S182" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="183" spans="1:19">
@@ -25418,16 +25970,16 @@
         <v>0.91900000000000004</v>
       </c>
       <c r="P183" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q183" s="3">
         <v>-7900</v>
       </c>
       <c r="R183" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S183" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="184" spans="1:19">
@@ -25477,16 +26029,16 @@
         <v>0.92300000000000004</v>
       </c>
       <c r="P184" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q184" s="2">
         <v>-4100</v>
       </c>
       <c r="R184" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S184" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="185" spans="1:19">
@@ -25536,16 +26088,16 @@
         <v>1.0209999999999999</v>
       </c>
       <c r="P185" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q185" s="3">
         <v>1100</v>
       </c>
       <c r="R185" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S185" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="186" spans="1:19">
@@ -25595,16 +26147,16 @@
         <v>1.0880000000000001</v>
       </c>
       <c r="P186" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q186" s="2">
         <v>6100</v>
       </c>
       <c r="R186" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S186" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="187" spans="1:19">
@@ -25654,16 +26206,16 @@
         <v>0.89</v>
       </c>
       <c r="P187" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q187" s="3">
         <v>-4800</v>
       </c>
       <c r="R187" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S187" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="188" spans="1:19">
@@ -25713,16 +26265,16 @@
         <v>0.86799999999999999</v>
       </c>
       <c r="P188" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q188" s="2">
         <v>-5500</v>
       </c>
       <c r="R188" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S188" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="189" spans="1:19">
@@ -25772,16 +26324,16 @@
         <v>0.9</v>
       </c>
       <c r="P189" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q189" s="3">
         <v>-4400</v>
       </c>
       <c r="R189" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S189" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="190" spans="1:19">
@@ -25831,16 +26383,16 @@
         <v>0.99</v>
       </c>
       <c r="P190" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q190" s="2">
         <v>-300</v>
       </c>
       <c r="R190" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S190" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="191" spans="1:19">
@@ -25890,16 +26442,16 @@
         <v>0.85799999999999998</v>
       </c>
       <c r="P191" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q191" s="3">
         <v>-8700</v>
       </c>
       <c r="R191" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S191" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="192" spans="1:19">
@@ -25949,16 +26501,16 @@
         <v>0.97499999999999998</v>
       </c>
       <c r="P192" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q192" s="2">
         <v>-900</v>
       </c>
       <c r="R192" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S192" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="193" spans="1:19">
@@ -26008,16 +26560,16 @@
         <v>0.88500000000000001</v>
       </c>
       <c r="P193" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q193" s="3">
         <v>-4800</v>
       </c>
       <c r="R193" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S193" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="194" spans="1:19">
@@ -26067,16 +26619,16 @@
         <v>1.0089999999999999</v>
       </c>
       <c r="P194" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q194" s="2">
         <v>400</v>
       </c>
       <c r="R194" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S194" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="195" spans="1:19">
@@ -26126,16 +26678,16 @@
         <v>0.92</v>
       </c>
       <c r="P195" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q195" s="3">
         <v>-2400</v>
       </c>
       <c r="R195" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S195" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="196" spans="1:19">
@@ -26185,16 +26737,16 @@
         <v>0.86399999999999999</v>
       </c>
       <c r="P196" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q196" s="2">
         <v>-3400</v>
       </c>
       <c r="R196" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S196" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="197" spans="1:19">
@@ -26244,16 +26796,16 @@
         <v>0.83599999999999997</v>
       </c>
       <c r="P197" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q197" s="3">
         <v>-5900</v>
       </c>
       <c r="R197" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S197" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="198" spans="1:19">
@@ -26303,16 +26855,16 @@
         <v>0.85499999999999998</v>
       </c>
       <c r="P198" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q198" s="2">
         <v>-6100</v>
       </c>
       <c r="R198" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S198" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="199" spans="1:19">
@@ -26362,16 +26914,16 @@
         <v>0.88500000000000001</v>
       </c>
       <c r="P199" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q199" s="3">
         <v>-6900</v>
       </c>
       <c r="R199" s="3" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S199" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="200" spans="1:19">
@@ -26421,16 +26973,16 @@
         <v>0.997</v>
       </c>
       <c r="P200" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q200" s="2">
         <v>-100</v>
       </c>
       <c r="R200" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S200" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="201" spans="1:19">
@@ -26480,16 +27032,16 @@
         <v>1.167</v>
       </c>
       <c r="P201" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q201" s="3">
         <v>7500</v>
       </c>
       <c r="R201" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S201" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="202" spans="1:19">
@@ -26539,16 +27091,16 @@
         <v>1.05</v>
       </c>
       <c r="P202" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q202" s="2">
         <v>1800</v>
       </c>
       <c r="R202" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S202" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="203" spans="1:19">
@@ -26598,16 +27150,16 @@
         <v>0.876</v>
       </c>
       <c r="P203" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q203" s="3">
         <v>-3100</v>
       </c>
       <c r="R203" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S203" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="204" spans="1:19">
@@ -26657,16 +27209,16 @@
         <v>1.014</v>
       </c>
       <c r="P204" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q204" s="2">
         <v>400</v>
       </c>
       <c r="R204" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S204" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="205" spans="1:19">
@@ -26716,16 +27268,16 @@
         <v>0.94</v>
       </c>
       <c r="P205" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q205" s="3">
         <v>-2500</v>
       </c>
       <c r="R205" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S205" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="206" spans="1:19">
@@ -26775,16 +27327,16 @@
         <v>1.034</v>
       </c>
       <c r="P206" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q206" s="2">
         <v>1200</v>
       </c>
       <c r="R206" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S206" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="207" spans="1:19">
@@ -26834,16 +27386,16 @@
         <v>0.86799999999999999</v>
       </c>
       <c r="P207" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q207" s="3">
         <v>-5500</v>
       </c>
       <c r="R207" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S207" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="208" spans="1:19">
@@ -26893,16 +27445,16 @@
         <v>0.86699999999999999</v>
       </c>
       <c r="P208" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q208" s="2">
         <v>-6000</v>
       </c>
       <c r="R208" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S208" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="209" spans="1:19">
@@ -26952,16 +27504,16 @@
         <v>0.91500000000000004</v>
       </c>
       <c r="P209" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q209" s="3">
         <v>-4600</v>
       </c>
       <c r="R209" s="3" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S209" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="210" spans="1:19">
@@ -27011,16 +27563,16 @@
         <v>0.873</v>
       </c>
       <c r="P210" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q210" s="2">
         <v>-3800</v>
       </c>
       <c r="R210" s="2" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S210" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="211" spans="1:19">
@@ -27070,16 +27622,16 @@
         <v>1.0169999999999999</v>
       </c>
       <c r="P211" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q211" s="3">
         <v>500</v>
       </c>
       <c r="R211" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S211" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="212" spans="1:19">
@@ -27129,16 +27681,16 @@
         <v>1</v>
       </c>
       <c r="P212" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q212" s="2">
         <v>0</v>
       </c>
       <c r="R212" s="2" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S212" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="213" spans="1:19">
@@ -27188,16 +27740,16 @@
         <v>0.97499999999999998</v>
       </c>
       <c r="P213" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q213" s="3">
         <v>-900</v>
       </c>
       <c r="R213" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S213" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="214" spans="1:19">
@@ -27247,16 +27799,16 @@
         <v>1.0409999999999999</v>
       </c>
       <c r="P214" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q214" s="2">
         <v>1200</v>
       </c>
       <c r="R214" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S214" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="215" spans="1:19">
@@ -27306,16 +27858,16 @@
         <v>1.19</v>
       </c>
       <c r="P215" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q215" s="3">
         <v>5700</v>
       </c>
       <c r="R215" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S215" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="216" spans="1:19">
@@ -27365,16 +27917,16 @@
         <v>0.90700000000000003</v>
       </c>
       <c r="P216" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q216" s="2">
         <v>-5000</v>
       </c>
       <c r="R216" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S216" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="217" spans="1:19">
@@ -27424,16 +27976,16 @@
         <v>0.94099999999999995</v>
       </c>
       <c r="P217" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q217" s="3">
         <v>-3500</v>
       </c>
       <c r="R217" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S217" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="218" spans="1:19">
@@ -27483,16 +28035,16 @@
         <v>0.94599999999999995</v>
       </c>
       <c r="P218" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q218" s="2">
         <v>-1300</v>
       </c>
       <c r="R218" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S218" s="2" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="219" spans="1:19">
@@ -27518,7 +28070,7 @@
         <v>28</v>
       </c>
       <c r="H219" s="3" t="s">
-        <v>641</v>
+        <v>658</v>
       </c>
       <c r="I219" s="3">
         <v>3.6</v>
@@ -27542,16 +28094,16 @@
         <v>0.94599999999999995</v>
       </c>
       <c r="P219" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q219" s="3">
         <v>-1900</v>
       </c>
       <c r="R219" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S219" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="220" spans="1:19">
@@ -27601,16 +28153,16 @@
         <v>0.95499999999999996</v>
       </c>
       <c r="P220" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q220" s="2">
         <v>-2500</v>
       </c>
       <c r="R220" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S220" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="221" spans="1:19">
@@ -27660,16 +28212,16 @@
         <v>0.95899999999999996</v>
       </c>
       <c r="P221" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q221" s="3">
         <v>-1800</v>
       </c>
       <c r="R221" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S221" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="222" spans="1:19">
@@ -27719,16 +28271,16 @@
         <v>0.92800000000000005</v>
       </c>
       <c r="P222" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q222" s="2">
         <v>-5200</v>
       </c>
       <c r="R222" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S222" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="223" spans="1:19">
@@ -27778,16 +28330,16 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="P223" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q223" s="3">
         <v>2700</v>
       </c>
       <c r="R223" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S223" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="224" spans="1:19">
@@ -27837,16 +28389,16 @@
         <v>0.96099999999999997</v>
       </c>
       <c r="P224" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q224" s="2">
         <v>-1700</v>
       </c>
       <c r="R224" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S224" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="225" spans="1:19">
@@ -27896,16 +28448,16 @@
         <v>0.97699999999999998</v>
       </c>
       <c r="P225" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q225" s="3">
         <v>-2000</v>
       </c>
       <c r="R225" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S225" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="226" spans="1:19">
@@ -27955,16 +28507,16 @@
         <v>0.89900000000000002</v>
       </c>
       <c r="P226" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q226" s="2">
         <v>-7600</v>
       </c>
       <c r="R226" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S226" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="227" spans="1:19">
@@ -28014,16 +28566,16 @@
         <v>0.98299999999999998</v>
       </c>
       <c r="P227" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q227" s="3">
         <v>-2000</v>
       </c>
       <c r="R227" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S227" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="228" spans="1:19">
@@ -28049,7 +28601,7 @@
         <v>21</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>642</v>
+        <v>659</v>
       </c>
       <c r="I228" s="2">
         <v>6</v>
@@ -28073,16 +28625,16 @@
         <v>0.77800000000000002</v>
       </c>
       <c r="P228" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q228" s="2">
         <v>-16800</v>
       </c>
       <c r="R228" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S228" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="229" spans="1:19">
@@ -28132,16 +28684,16 @@
         <v>0.88500000000000001</v>
       </c>
       <c r="P229" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q229" s="3">
         <v>-8700</v>
       </c>
       <c r="R229" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S229" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="230" spans="1:19">
@@ -28191,16 +28743,16 @@
         <v>0.89600000000000002</v>
       </c>
       <c r="P230" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q230" s="2">
         <v>-6200</v>
       </c>
       <c r="R230" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S230" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="231" spans="1:19">
@@ -28250,16 +28802,16 @@
         <v>0.94199999999999995</v>
       </c>
       <c r="P231" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q231" s="3">
         <v>-8300</v>
       </c>
       <c r="R231" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S231" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="232" spans="1:19">
@@ -28309,16 +28861,16 @@
         <v>1.056</v>
       </c>
       <c r="P232" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q232" s="2">
         <v>3700</v>
       </c>
       <c r="R232" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S232" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="233" spans="1:19">
@@ -28368,16 +28920,16 @@
         <v>0.85899999999999999</v>
       </c>
       <c r="P233" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q233" s="3">
         <v>-12300</v>
       </c>
       <c r="R233" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S233" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="234" spans="1:19">
@@ -28427,16 +28979,16 @@
         <v>0.78600000000000003</v>
       </c>
       <c r="P234" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q234" s="2">
         <v>-24900</v>
       </c>
       <c r="R234" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S234" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="235" spans="1:19">
@@ -28486,16 +29038,16 @@
         <v>0.83599999999999997</v>
       </c>
       <c r="P235" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q235" s="3">
         <v>-7000</v>
       </c>
       <c r="R235" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S235" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="236" spans="1:19">
@@ -28545,16 +29097,16 @@
         <v>1.012</v>
       </c>
       <c r="P236" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q236" s="2">
         <v>900</v>
       </c>
       <c r="R236" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S236" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="237" spans="1:19">
@@ -28604,16 +29156,16 @@
         <v>1.0149999999999999</v>
       </c>
       <c r="P237" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q237" s="3">
         <v>1200</v>
       </c>
       <c r="R237" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S237" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="238" spans="1:19">
@@ -28663,16 +29215,16 @@
         <v>1.1830000000000001</v>
       </c>
       <c r="P238" s="2" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q238" s="2">
         <v>9900</v>
       </c>
       <c r="R238" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S238" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="239" spans="1:19">
@@ -28722,16 +29274,16 @@
         <v>0.872</v>
       </c>
       <c r="P239" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q239" s="3">
         <v>-13800</v>
       </c>
       <c r="R239" s="3" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S239" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="240" spans="1:19">
@@ -28781,16 +29333,16 @@
         <v>0.89400000000000002</v>
       </c>
       <c r="P240" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q240" s="2">
         <v>-6900</v>
       </c>
       <c r="R240" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S240" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="241" spans="1:19">
@@ -28840,16 +29392,16 @@
         <v>1.0309999999999999</v>
       </c>
       <c r="P241" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q241" s="3">
         <v>1900</v>
       </c>
       <c r="R241" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S241" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="242" spans="1:19">
@@ -28899,16 +29451,16 @@
         <v>0.82599999999999996</v>
       </c>
       <c r="P242" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q242" s="2">
         <v>-13600</v>
       </c>
       <c r="R242" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S242" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="243" spans="1:19">
@@ -28958,16 +29510,16 @@
         <v>0.98099999999999998</v>
       </c>
       <c r="P243" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q243" s="3">
         <v>-600</v>
       </c>
       <c r="R243" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S243" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="244" spans="1:19">
@@ -29017,16 +29569,16 @@
         <v>0.93700000000000006</v>
       </c>
       <c r="P244" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q244" s="2">
         <v>-4000</v>
       </c>
       <c r="R244" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S244" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="245" spans="1:19">
@@ -29076,16 +29628,16 @@
         <v>0.91300000000000003</v>
       </c>
       <c r="P245" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q245" s="3">
         <v>-6600</v>
       </c>
       <c r="R245" s="3" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S245" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="246" spans="1:19">
@@ -29135,16 +29687,16 @@
         <v>1.1339999999999999</v>
       </c>
       <c r="P246" s="2" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q246" s="2">
         <v>12900</v>
       </c>
       <c r="R246" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S246" s="2" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="247" spans="1:19">
@@ -29194,16 +29746,16 @@
         <v>0.89400000000000002</v>
       </c>
       <c r="P247" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q247" s="3">
         <v>-9500</v>
       </c>
       <c r="R247" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S247" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="248" spans="1:19">
@@ -29253,16 +29805,16 @@
         <v>0.85299999999999998</v>
       </c>
       <c r="P248" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q248" s="2">
         <v>-11100</v>
       </c>
       <c r="R248" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S248" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="249" spans="1:19">
@@ -29312,16 +29864,16 @@
         <v>1.0549999999999999</v>
       </c>
       <c r="P249" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q249" s="3">
         <v>3100</v>
       </c>
       <c r="R249" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S249" s="3" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="250" spans="1:19">
@@ -29371,16 +29923,16 @@
         <v>0.879</v>
       </c>
       <c r="P250" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q250" s="2">
         <v>-7600</v>
       </c>
       <c r="R250" s="2" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="S250" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="251" spans="1:19">
@@ -29430,16 +29982,16 @@
         <v>0.745</v>
       </c>
       <c r="P251" s="3" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q251" s="3">
         <v>-24500</v>
       </c>
       <c r="R251" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S251" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="252" spans="1:19">
@@ -29489,16 +30041,16 @@
         <v>0.79400000000000004</v>
       </c>
       <c r="P252" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q252" s="2">
         <v>-9700</v>
       </c>
       <c r="R252" s="2" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S252" s="2" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="253" spans="1:19">
@@ -29548,16 +30100,16 @@
         <v>0.98699999999999999</v>
       </c>
       <c r="P253" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q253" s="3">
         <v>-400</v>
       </c>
       <c r="R253" s="3" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
       <c r="S253" s="3" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="254" spans="1:19">
@@ -29607,16 +30159,16 @@
         <v>0.84899999999999998</v>
       </c>
       <c r="P254" s="2" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
       <c r="Q254" s="2">
         <v>-10000</v>
       </c>
       <c r="R254" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S254" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="255" spans="1:19">
@@ -29666,16 +30218,16 @@
         <v>1.0680000000000001</v>
       </c>
       <c r="P255" s="3" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q255" s="3">
         <v>3100</v>
       </c>
       <c r="R255" s="3" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S255" s="3" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="256" spans="1:19">
@@ -29725,16 +30277,16 @@
         <v>1.0589999999999999</v>
       </c>
       <c r="P256" s="2" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="Q256" s="2">
         <v>3300</v>
       </c>
       <c r="R256" s="2" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
       <c r="S256" s="2" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="257" spans="1:19">
@@ -29784,16 +30336,16 @@
         <v>1.155</v>
       </c>
       <c r="P257" s="3" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="Q257" s="3">
         <v>11700</v>
       </c>
       <c r="R257" s="3" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="S257" s="3" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>
